--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,212 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126125723</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>421434</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6962287</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126133773</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79561</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>421831</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6962414</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>126125723</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126133773</v>
       </c>
       <c r="B7" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1142,7 +1142,7 @@
         <v>126125723</v>
       </c>
       <c r="B6" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126133773</v>
       </c>
       <c r="B7" t="n">
-        <v>79562</v>
+        <v>79566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,6 +1343,2347 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126348530</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>421907</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6962257</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126348520</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>421846</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6962154</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126348525</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>422007</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6962244</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126348518</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>421794</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6962250</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126348528</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>421918</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6962269</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126348522</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>421895</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6962187</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126348516</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>421720</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6962266</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126348517</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>421753</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6962274</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126348512</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>421437</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6962452</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126348523</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>421904</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6962234</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126348531</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>421867</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6962255</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126348526</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>421990</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6962251</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126348529</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>421911</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6962272</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126348542</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>421390</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6962623</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126348527</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>421924</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6962309</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126348515</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>421542</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6962275</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126348519</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>421839</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6962191</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126348514</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>421522</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6962292</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126348524</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>421923</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6962232</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126348580</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91260</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>421840</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6962183</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126348532</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>421731</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6962317</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126348513</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>421488</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6962412</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126348521</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57656</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>421869</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6962131</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126348514</v>
+        <v>126348580</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421522</v>
+        <v>421840</v>
       </c>
       <c r="R25" t="n">
-        <v>6962292</v>
+        <v>6962183</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,11 +3150,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3181,7 +3176,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126348524</v>
+        <v>126348514</v>
       </c>
       <c r="B26" t="n">
         <v>57656</v>
@@ -3216,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421923</v>
+        <v>421522</v>
       </c>
       <c r="R26" t="n">
-        <v>6962232</v>
+        <v>6962292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3283,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348580</v>
+        <v>126348524</v>
       </c>
       <c r="B27" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421840</v>
+        <v>421923</v>
       </c>
       <c r="R27" t="n">
-        <v>6962183</v>
+        <v>6962232</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,6 +3349,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126348580</v>
+        <v>126348514</v>
       </c>
       <c r="B25" t="n">
-        <v>91260</v>
+        <v>57656</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421840</v>
+        <v>421522</v>
       </c>
       <c r="R25" t="n">
-        <v>6962183</v>
+        <v>6962292</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3150,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,7 +3181,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126348514</v>
+        <v>126348524</v>
       </c>
       <c r="B26" t="n">
         <v>57656</v>
@@ -3211,10 +3216,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421522</v>
+        <v>421923</v>
       </c>
       <c r="R26" t="n">
-        <v>6962292</v>
+        <v>6962232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3283,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348524</v>
+        <v>126348580</v>
       </c>
       <c r="B27" t="n">
-        <v>57656</v>
+        <v>91260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3289,21 +3294,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3313,10 +3318,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421923</v>
+        <v>421840</v>
       </c>
       <c r="R27" t="n">
-        <v>6962232</v>
+        <v>6962183</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3349,11 +3354,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -1142,7 +1142,7 @@
         <v>126125723</v>
       </c>
       <c r="B6" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>126133773</v>
       </c>
       <c r="B7" t="n">
-        <v>79566</v>
+        <v>79569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
         <v>126348530</v>
       </c>
       <c r="B8" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348520</v>
+        <v>126348525</v>
       </c>
       <c r="B9" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421846</v>
+        <v>422007</v>
       </c>
       <c r="R9" t="n">
-        <v>6962154</v>
+        <v>6962244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348525</v>
+        <v>126348520</v>
       </c>
       <c r="B10" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422007</v>
+        <v>421846</v>
       </c>
       <c r="R10" t="n">
-        <v>6962244</v>
+        <v>6962154</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348518</v>
+        <v>126348528</v>
       </c>
       <c r="B11" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421794</v>
+        <v>421918</v>
       </c>
       <c r="R11" t="n">
-        <v>6962250</v>
+        <v>6962269</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,10 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348528</v>
+        <v>126348518</v>
       </c>
       <c r="B12" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421918</v>
+        <v>421794</v>
       </c>
       <c r="R12" t="n">
-        <v>6962269</v>
+        <v>6962250</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1858,7 +1858,7 @@
         <v>126348522</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>126348516</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>126348517</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>126348512</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>126348523</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>126348531</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>126348526</v>
       </c>
       <c r="B19" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2572,7 +2572,7 @@
         <v>126348529</v>
       </c>
       <c r="B20" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>126348542</v>
       </c>
       <c r="B21" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2773,10 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126348527</v>
+        <v>126348519</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421924</v>
+        <v>421839</v>
       </c>
       <c r="R22" t="n">
-        <v>6962309</v>
+        <v>6962191</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,10 +2875,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126348515</v>
+        <v>126348527</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421542</v>
+        <v>421924</v>
       </c>
       <c r="R23" t="n">
-        <v>6962275</v>
+        <v>6962309</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,10 +2977,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126348519</v>
+        <v>126348515</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421839</v>
+        <v>421542</v>
       </c>
       <c r="R24" t="n">
-        <v>6962191</v>
+        <v>6962275</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3079,10 +3079,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126348514</v>
+        <v>126348580</v>
       </c>
       <c r="B25" t="n">
-        <v>57656</v>
+        <v>91263</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3090,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421522</v>
+        <v>421840</v>
       </c>
       <c r="R25" t="n">
-        <v>6962292</v>
+        <v>6962183</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,11 +3150,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3184,7 +3179,7 @@
         <v>126348524</v>
       </c>
       <c r="B26" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3283,10 +3278,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348580</v>
+        <v>126348514</v>
       </c>
       <c r="B27" t="n">
-        <v>91260</v>
+        <v>57657</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3294,21 +3289,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421840</v>
+        <v>421522</v>
       </c>
       <c r="R27" t="n">
-        <v>6962183</v>
+        <v>6962292</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3354,6 +3349,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3383,7 +3383,7 @@
         <v>126348532</v>
       </c>
       <c r="B28" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>126348513</v>
       </c>
       <c r="B29" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>126348521</v>
       </c>
       <c r="B30" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -1651,7 +1651,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348528</v>
+        <v>126348518</v>
       </c>
       <c r="B11" t="n">
         <v>57657</v>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421918</v>
+        <v>421794</v>
       </c>
       <c r="R11" t="n">
-        <v>6962269</v>
+        <v>6962250</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348518</v>
+        <v>126348528</v>
       </c>
       <c r="B12" t="n">
         <v>57657</v>
@@ -1788,10 +1788,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421794</v>
+        <v>421918</v>
       </c>
       <c r="R12" t="n">
-        <v>6962250</v>
+        <v>6962269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2773,7 +2773,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126348519</v>
+        <v>126348527</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421839</v>
+        <v>421924</v>
       </c>
       <c r="R22" t="n">
-        <v>6962191</v>
+        <v>6962309</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126348527</v>
+        <v>126348515</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421924</v>
+        <v>421542</v>
       </c>
       <c r="R23" t="n">
-        <v>6962309</v>
+        <v>6962275</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126348515</v>
+        <v>126348519</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421542</v>
+        <v>421839</v>
       </c>
       <c r="R24" t="n">
-        <v>6962275</v>
+        <v>6962191</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126348513</v>
+        <v>126348521</v>
       </c>
       <c r="B29" t="n">
         <v>57657</v>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421488</v>
+        <v>421869</v>
       </c>
       <c r="R29" t="n">
-        <v>6962412</v>
+        <v>6962131</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,7 +3584,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126348521</v>
+        <v>126348513</v>
       </c>
       <c r="B30" t="n">
         <v>57657</v>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421869</v>
+        <v>421488</v>
       </c>
       <c r="R30" t="n">
-        <v>6962131</v>
+        <v>6962412</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -1447,7 +1447,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348525</v>
+        <v>126348520</v>
       </c>
       <c r="B9" t="n">
         <v>57657</v>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422007</v>
+        <v>421846</v>
       </c>
       <c r="R9" t="n">
-        <v>6962244</v>
+        <v>6962154</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348520</v>
+        <v>126348525</v>
       </c>
       <c r="B10" t="n">
         <v>57657</v>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>421846</v>
+        <v>422007</v>
       </c>
       <c r="R10" t="n">
-        <v>6962154</v>
+        <v>6962244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -3176,7 +3176,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126348524</v>
+        <v>126348514</v>
       </c>
       <c r="B26" t="n">
         <v>57657</v>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421923</v>
+        <v>421522</v>
       </c>
       <c r="R26" t="n">
-        <v>6962232</v>
+        <v>6962292</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,7 +3278,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348514</v>
+        <v>126348524</v>
       </c>
       <c r="B27" t="n">
         <v>57657</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421522</v>
+        <v>421923</v>
       </c>
       <c r="R27" t="n">
-        <v>6962292</v>
+        <v>6962232</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126348521</v>
+        <v>126348513</v>
       </c>
       <c r="B29" t="n">
         <v>57657</v>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421869</v>
+        <v>421488</v>
       </c>
       <c r="R29" t="n">
-        <v>6962131</v>
+        <v>6962412</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,7 +3584,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126348513</v>
+        <v>126348521</v>
       </c>
       <c r="B30" t="n">
         <v>57657</v>
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421488</v>
+        <v>421869</v>
       </c>
       <c r="R30" t="n">
-        <v>6962412</v>
+        <v>6962131</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -2773,7 +2773,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126348527</v>
+        <v>126348515</v>
       </c>
       <c r="B22" t="n">
         <v>57657</v>
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421924</v>
+        <v>421542</v>
       </c>
       <c r="R22" t="n">
-        <v>6962309</v>
+        <v>6962275</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126348515</v>
+        <v>126348519</v>
       </c>
       <c r="B23" t="n">
         <v>57657</v>
@@ -2910,10 +2910,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421542</v>
+        <v>421839</v>
       </c>
       <c r="R23" t="n">
-        <v>6962275</v>
+        <v>6962191</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126348519</v>
+        <v>126348527</v>
       </c>
       <c r="B24" t="n">
         <v>57657</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421839</v>
+        <v>421924</v>
       </c>
       <c r="R24" t="n">
-        <v>6962191</v>
+        <v>6962309</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7000937</v>
+        <v>7000935</v>
       </c>
       <c r="B2" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>421808.6270007952</v>
+        <v>421808</v>
       </c>
       <c r="R2" t="n">
-        <v>6962336.236659291</v>
+        <v>6962190</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2013-08-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7000935</v>
+        <v>7000937</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>421808.3620127374</v>
+        <v>421809</v>
       </c>
       <c r="R3" t="n">
-        <v>6962190.165434634</v>
+        <v>6962336</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2013-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-08-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7000936</v>
+        <v>7000934</v>
       </c>
       <c r="B4" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>421722.5499542892</v>
+        <v>421880</v>
       </c>
       <c r="R4" t="n">
-        <v>6962495.804066436</v>
+        <v>6962152</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2013-08-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7000934</v>
+        <v>91847279</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,34 +989,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Råberget, Hjd</t>
+          <t>Jämtlands län, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>421879.9063342992</v>
+        <v>421304</v>
       </c>
       <c r="R5" t="n">
-        <v>6962151.829397733</v>
+        <v>6962350</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,22 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2013-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-06-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2013-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-10-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,72 +1063,64 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Via Erland Lindblad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126125723</v>
+        <v>7000936</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>92083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1503</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>421434</v>
+        <v>421723</v>
       </c>
       <c r="R6" t="n">
-        <v>6962287</v>
+        <v>6962496</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2013-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2013-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,22 +1164,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
+          <t>Hugo Ström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126133773</v>
+        <v>126125633</v>
       </c>
       <c r="B7" t="n">
-        <v>79569</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,26 +1191,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1282,13 +1223,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>421831</v>
+        <v>421861</v>
       </c>
       <c r="R7" t="n">
-        <v>6962414</v>
+        <v>6962444</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1267,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1345,10 +1285,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126348530</v>
+        <v>126125723</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,19 +1314,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>421907</v>
+        <v>421434</v>
       </c>
       <c r="R8" t="n">
-        <v>6962257</v>
+        <v>6962287</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1410,17 +1358,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1435,22 +1378,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126348520</v>
+        <v>126348511</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,16 +1419,24 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Råberget, Hjd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>421846</v>
+        <v>421432</v>
       </c>
       <c r="R9" t="n">
-        <v>6962154</v>
+        <v>6962635</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,7 +1473,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Sannolikt tidigare tretå-bohål, ca 1,6m upp i bruten gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,10 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126348525</v>
+        <v>126348512</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1584,10 +1535,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422007</v>
+        <v>421437</v>
       </c>
       <c r="R10" t="n">
-        <v>6962244</v>
+        <v>6962452</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1651,10 +1602,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126348518</v>
+        <v>126348513</v>
       </c>
       <c r="B11" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1686,10 +1637,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>421794</v>
+        <v>421488</v>
       </c>
       <c r="R11" t="n">
-        <v>6962250</v>
+        <v>6962412</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1726,7 +1677,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1753,10 +1704,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126348528</v>
+        <v>126348514</v>
       </c>
       <c r="B12" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>421918</v>
+        <v>421522</v>
       </c>
       <c r="R12" t="n">
-        <v>6962269</v>
+        <v>6962292</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,10 +1806,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126348522</v>
+        <v>126348515</v>
       </c>
       <c r="B13" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1890,10 +1841,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>421895</v>
+        <v>421542</v>
       </c>
       <c r="R13" t="n">
-        <v>6962187</v>
+        <v>6962275</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1930,7 +1881,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1960,7 +1911,7 @@
         <v>126348516</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2062,7 +2013,7 @@
         <v>126348517</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,10 +2112,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126348512</v>
+        <v>126348518</v>
       </c>
       <c r="B16" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,10 +2147,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>421437</v>
+        <v>421794</v>
       </c>
       <c r="R16" t="n">
-        <v>6962452</v>
+        <v>6962250</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2236,7 +2187,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2263,10 +2214,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126348523</v>
+        <v>126348519</v>
       </c>
       <c r="B17" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2298,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>421904</v>
+        <v>421839</v>
       </c>
       <c r="R17" t="n">
-        <v>6962234</v>
+        <v>6962191</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2338,7 +2289,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,10 +2316,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126348531</v>
+        <v>126348520</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,10 +2351,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>421867</v>
+        <v>421846</v>
       </c>
       <c r="R18" t="n">
-        <v>6962255</v>
+        <v>6962154</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2440,7 +2391,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2467,10 +2418,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126348526</v>
+        <v>126348521</v>
       </c>
       <c r="B19" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2502,10 +2453,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>421990</v>
+        <v>421869</v>
       </c>
       <c r="R19" t="n">
-        <v>6962251</v>
+        <v>6962131</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2542,7 +2493,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2569,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126348529</v>
+        <v>126348522</v>
       </c>
       <c r="B20" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2604,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>421911</v>
+        <v>421895</v>
       </c>
       <c r="R20" t="n">
-        <v>6962272</v>
+        <v>6962187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2644,7 +2595,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2671,10 +2622,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126348542</v>
+        <v>126348523</v>
       </c>
       <c r="B21" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2706,10 +2657,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>421390</v>
+        <v>421904</v>
       </c>
       <c r="R21" t="n">
-        <v>6962623</v>
+        <v>6962234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2746,7 +2697,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2773,10 +2724,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126348527</v>
+        <v>126348524</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2808,10 +2759,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>421924</v>
+        <v>421923</v>
       </c>
       <c r="R22" t="n">
-        <v>6962309</v>
+        <v>6962232</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2848,7 +2799,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2875,10 +2826,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126348515</v>
+        <v>126348525</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2910,10 +2861,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>421542</v>
+        <v>422007</v>
       </c>
       <c r="R23" t="n">
-        <v>6962275</v>
+        <v>6962244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2977,10 +2928,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126348519</v>
+        <v>126348526</v>
       </c>
       <c r="B24" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3012,10 +2963,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>421839</v>
+        <v>421990</v>
       </c>
       <c r="R24" t="n">
-        <v>6962191</v>
+        <v>6962251</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3052,7 +3003,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3079,10 +3030,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126348580</v>
+        <v>126348527</v>
       </c>
       <c r="B25" t="n">
-        <v>91263</v>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3090,21 +3041,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3114,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>421840</v>
+        <v>421924</v>
       </c>
       <c r="R25" t="n">
-        <v>6962183</v>
+        <v>6962309</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3150,6 +3101,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3176,10 +3132,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126348514</v>
+        <v>126348528</v>
       </c>
       <c r="B26" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3211,10 +3167,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>421522</v>
+        <v>421918</v>
       </c>
       <c r="R26" t="n">
-        <v>6962292</v>
+        <v>6962269</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3278,10 +3234,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126348524</v>
+        <v>126348529</v>
       </c>
       <c r="B27" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3313,10 +3269,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>421923</v>
+        <v>421911</v>
       </c>
       <c r="R27" t="n">
-        <v>6962232</v>
+        <v>6962272</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3353,7 +3309,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3380,10 +3336,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126348532</v>
+        <v>126348530</v>
       </c>
       <c r="B28" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3415,10 +3371,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>421731</v>
+        <v>421907</v>
       </c>
       <c r="R28" t="n">
-        <v>6962317</v>
+        <v>6962257</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3455,7 +3411,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3482,10 +3438,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126348513</v>
+        <v>126348531</v>
       </c>
       <c r="B29" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3517,10 +3473,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>421488</v>
+        <v>421867</v>
       </c>
       <c r="R29" t="n">
-        <v>6962412</v>
+        <v>6962255</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3557,7 +3513,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3584,10 +3540,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126348521</v>
+        <v>126348532</v>
       </c>
       <c r="B30" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3619,10 +3575,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>421869</v>
+        <v>421731</v>
       </c>
       <c r="R30" t="n">
-        <v>6962131</v>
+        <v>6962317</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3659,7 +3615,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3683,6 +3639,209 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126348542</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>421390</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6962623</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126133773</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Råberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>421831</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6962414</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27571-2025 artfynd.xlsx
+++ b/artfynd/A 27571-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000935</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000937</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000934</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91847279</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7000936</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1282,6 +1312,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125633</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126125723</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1497,6 +1537,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348511</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,6 +1644,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348512</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1701,6 +1751,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348513</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348514</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348515</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2007,6 +2072,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348516</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2109,6 +2179,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348517</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2211,6 +2286,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348518</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2313,6 +2393,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348519</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2415,6 +2500,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348520</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348521</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2619,6 +2714,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348522</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2721,6 +2821,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348523</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2823,6 +2928,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348524</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2925,6 +3035,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348525</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3027,6 +3142,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348526</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3129,6 +3249,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348527</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3231,6 +3356,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348528</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3333,6 +3463,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348529</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3435,6 +3570,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348530</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3537,6 +3677,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348531</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,6 +3784,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348532</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3741,6 +3891,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126348542</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3842,8 +3997,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126133773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>